--- a/data/externalStats/File1/RPT_RPT6577630625872WM_externalStats.xlsx
+++ b/data/externalStats/File1/RPT_RPT6577630625872WM_externalStats.xlsx
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>4927825.286656229</v>
+        <v>4927825.286071727</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>7094.223987863295</v>
@@ -2258,7 +2258,7 @@
         <v>556393.580935954</v>
       </c>
       <c r="AI27" s="56" t="n">
-        <v>827.1029214485164</v>
+        <v>827.1029214485163</v>
       </c>
       <c r="AK27" s="123" t="n">
         <v>3</v>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="AN28" s="58" t="n">
-        <v>3060.609005713498</v>
+        <v>3060.609005713499</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" thickBot="1">
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>198669.400700446</v>
+        <v>198669.4007004459</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>199.9395963677785</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>179592.8317901432</v>
+        <v>179592.8317715833</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>509.6993712707739</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="AN31" s="58" t="n">
-        <v>720.9506748454983</v>
+        <v>720.9506748454982</v>
       </c>
       <c r="AW31" s="77" t="n"/>
       <c r="AX31" s="78" t="n"/>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>142712.7099814788</v>
+        <v>142712.7093633207</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>1938.318957923954</v>
@@ -2700,7 +2700,7 @@
         <v>122337.3954337064</v>
       </c>
       <c r="AI33" s="56" t="n">
-        <v>358.4698264140781</v>
+        <v>358.4698264140782</v>
       </c>
       <c r="AK33" s="123" t="n">
         <v>9</v>
@@ -2777,7 +2777,7 @@
         <v>119720.1244139953</v>
       </c>
       <c r="AI34" s="56" t="n">
-        <v>45.33514103688</v>
+        <v>45.33514103688001</v>
       </c>
       <c r="AK34" s="123" t="n">
         <v>10</v>
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>108001.2818473886</v>
+        <v>108001.2801948774</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>222.5593240475558</v>
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>77252.6286851506</v>
+        <v>77252.62868515062</v>
       </c>
       <c r="AI37" s="56" t="n">
-        <v>278.6758692628373</v>
+        <v>278.6758692628374</v>
       </c>
       <c r="AK37" s="123" t="n">
         <v>13</v>
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>69745.34687489273</v>
+        <v>69745.34681762784</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>203.9703763401057</v>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>5484218.867592182</v>
+        <v>5484218.867007682</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>12821.12275198584</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>1089329.097060542</v>
+        <v>1089329.097041982</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>6903.200315204283</v>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>318389.5251144413</v>
+        <v>318389.5251144412</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>245.2747374046585</v>
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>271672.0313373304</v>
+        <v>271672.0296419976</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>500.4368615867007</v>
@@ -4120,7 +4120,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>172405.0318301367</v>
+        <v>172405.0316900843</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>500.4178695794146</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>152589.5747412443</v>
+        <v>152589.5740804472</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>2102.862750485375</v>
@@ -4328,7 +4328,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="R58" s="131" t="n">
         <v>0</v>
@@ -4337,7 +4337,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="V58" s="130" t="n">
         <v>0</v>
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>99533.70582331822</v>
+        <v>99533.70574482233</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>296.8783488091591</v>
@@ -4406,7 +4406,7 @@
         <v>25.4948504607565</v>
       </c>
       <c r="P59" s="130" t="n">
-        <v>27.65663487526179</v>
+        <v>27.6566348752618</v>
       </c>
       <c r="Q59" s="131" t="n">
         <v>0</v>
@@ -4415,10 +4415,10 @@
         <v>0</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>0.6107794764899804</v>
+        <v>0.6107794764899805</v>
       </c>
       <c r="T59" s="132" t="n">
-        <v>28.26741435175177</v>
+        <v>28.26741435175178</v>
       </c>
       <c r="V59" s="130" t="n">
         <v>31.05175440243663</v>
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>80589.41319472338</v>
+        <v>80589.41309172791</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>142.7523736965244</v>
@@ -4487,7 +4487,7 @@
         <v>12.15752497820848</v>
       </c>
       <c r="P60" s="130" t="n">
-        <v>6.618249046619541</v>
+        <v>6.618249046619542</v>
       </c>
       <c r="Q60" s="131" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
         <v>0</v>
       </c>
       <c r="T60" s="132" t="n">
-        <v>6.618249046619541</v>
+        <v>6.618249046619542</v>
       </c>
       <c r="V60" s="130" t="n">
         <v>6.034114128367584</v>
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>74725.20829710716</v>
+        <v>74725.2082663402</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>255.6573809308344</v>
@@ -4568,13 +4568,13 @@
         <v>9893.16513563129</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>6228.776889941022</v>
+        <v>6228.776889941023</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>3999.114543167052</v>
+        <v>3999.114543167051</v>
       </c>
       <c r="R61" s="131" t="n">
-        <v>73.5852791072068</v>
+        <v>73.58527910720682</v>
       </c>
       <c r="S61" s="131" t="n">
         <v>0</v>
@@ -4583,13 +4583,13 @@
         <v>10301.47671221528</v>
       </c>
       <c r="V61" s="130" t="n">
-        <v>6447.101264258591</v>
+        <v>6447.10126425859</v>
       </c>
       <c r="W61" s="131" t="n">
         <v>4230.066745339464</v>
       </c>
       <c r="X61" s="131" t="n">
-        <v>77.66240762792478</v>
+        <v>77.66240762792476</v>
       </c>
       <c r="Y61" s="131" t="n">
         <v>0</v>
@@ -4649,13 +4649,13 @@
         <v>1051.558057647748</v>
       </c>
       <c r="P62" s="130" t="n">
-        <v>344.8677977438759</v>
+        <v>344.8677977438761</v>
       </c>
       <c r="Q62" s="131" t="n">
-        <v>695.6708181072373</v>
+        <v>695.6708181072372</v>
       </c>
       <c r="R62" s="131" t="n">
-        <v>4.376881306996877</v>
+        <v>4.376881306996878</v>
       </c>
       <c r="S62" s="131" t="n">
         <v>0</v>
@@ -4664,7 +4664,7 @@
         <v>1044.91549715811</v>
       </c>
       <c r="V62" s="130" t="n">
-        <v>337.2252462051626</v>
+        <v>337.2252462051625</v>
       </c>
       <c r="W62" s="131" t="n">
         <v>693.7423997998152</v>
@@ -4718,7 +4718,7 @@
         <v>2692.467611904198</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>2139.40980991461</v>
+        <v>2139.409809914607</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>34.42048685206299</v>
@@ -4727,22 +4727,22 @@
         <v>4055.662939861252</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>8921.960848532122</v>
+        <v>8921.960848532119</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>3161.62725325569</v>
+        <v>3161.627253255683</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>2604.953328398544</v>
+        <v>2604.953328398546</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>42.03577551248003</v>
+        <v>42.03577551248009</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>4367.592784770583</v>
+        <v>4367.592784770584</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>10176.2091419373</v>
+        <v>10176.20914193729</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>3718.424539440057</v>
@@ -4751,7 +4751,7 @@
         <v>3171.189177178967</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>51.03255827472313</v>
+        <v>51.03255827472316</v>
       </c>
       <c r="Y63" s="131" t="n">
         <v>4661.350612147648</v>
@@ -4768,7 +4768,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>69529.4815161007</v>
+        <v>69529.48151610068</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>199.0707660676643</v>
@@ -4820,10 +4820,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>4367.589286582866</v>
+        <v>4367.589286582867</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>4367.589286582866</v>
+        <v>4367.589286582867</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>55738.61394026375</v>
+        <v>55738.61394026374</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>151.7552846355375</v>
@@ -5045,16 +5045,16 @@
         <v>0</v>
       </c>
       <c r="J67" s="139" t="n">
-        <v>32665.80535718387</v>
+        <v>32665.80535718386</v>
       </c>
       <c r="K67" s="140" t="n">
-        <v>14983.8247713327</v>
+        <v>14983.82477133271</v>
       </c>
       <c r="L67" s="140" t="n">
         <v>202.3739864950116</v>
       </c>
       <c r="M67" s="140" t="n">
-        <v>552.1088310115438</v>
+        <v>552.1088310115437</v>
       </c>
       <c r="N67" s="141" t="n">
         <v>48404.11294602312</v>
@@ -5069,10 +5069,10 @@
         <v>142.2558187419964</v>
       </c>
       <c r="S67" s="140" t="n">
-        <v>529.4434178862318</v>
+        <v>529.4434178862319</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>40480.89080031734</v>
+        <v>40480.89080031735</v>
       </c>
       <c r="V67" s="139" t="n">
         <v>27700.89671012674</v>
@@ -5141,19 +5141,19 @@
         <v>72370.99438301698</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>39238.32152279546</v>
+        <v>39238.32152279547</v>
       </c>
       <c r="Q68" s="143" t="n">
         <v>17647.25318436719</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>262.2537546686801</v>
+        <v>262.2537546686802</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>4897.646982133305</v>
+        <v>4897.646982133306</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>66413.0647305475</v>
+        <v>66413.06473054751</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>38240.73362856136</v>
@@ -5747,10 +5747,10 @@
         <v>0</v>
       </c>
       <c r="M77" s="131" t="n">
-        <v>0.7494770222813295</v>
+        <v>0.7494770222813296</v>
       </c>
       <c r="N77" s="132" t="n">
-        <v>0.7494770222813295</v>
+        <v>0.7494770222813296</v>
       </c>
       <c r="P77" s="130" t="n">
         <v>0</v>
@@ -5762,10 +5762,10 @@
         <v>0</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>0.8356985266883199</v>
+        <v>0.8356985266883201</v>
       </c>
       <c r="T77" s="132" t="n">
-        <v>0.8356985266883199</v>
+        <v>0.8356985266883201</v>
       </c>
       <c r="V77" s="130" t="n">
         <v>0</v>
@@ -5777,10 +5777,10 @@
         <v>0</v>
       </c>
       <c r="Y77" s="131" t="n">
-        <v>0.8963748172115763</v>
+        <v>0.8963748172115764</v>
       </c>
       <c r="Z77" s="132" t="n">
-        <v>0.8963748172115763</v>
+        <v>0.8963748172115764</v>
       </c>
     </row>
     <row r="78">
@@ -5835,7 +5835,7 @@
         <v>19.96087013213621</v>
       </c>
       <c r="V78" s="130" t="n">
-        <v>22.02775740512094</v>
+        <v>22.02775740512093</v>
       </c>
       <c r="W78" s="131" t="n">
         <v>0</v>
@@ -5847,7 +5847,7 @@
         <v>0</v>
       </c>
       <c r="Z78" s="132" t="n">
-        <v>22.02775740512094</v>
+        <v>22.02775740512093</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
@@ -5872,13 +5872,13 @@
         <v>4433</v>
       </c>
       <c r="J79" s="130" t="n">
-        <v>2476.941695579429</v>
+        <v>2476.941695579428</v>
       </c>
       <c r="K79" s="131" t="n">
         <v>2849.092396586792</v>
       </c>
       <c r="L79" s="131" t="n">
-        <v>11.82289063599359</v>
+        <v>11.8228906359936</v>
       </c>
       <c r="M79" s="131" t="n">
         <v>0</v>
@@ -5887,10 +5887,10 @@
         <v>5337.856982802215</v>
       </c>
       <c r="P79" s="130" t="n">
-        <v>2558.682056625252</v>
+        <v>2558.682056625253</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>2925.262718709261</v>
+        <v>2925.262718709262</v>
       </c>
       <c r="R79" s="131" t="n">
         <v>12.15252135439121</v>
@@ -5899,10 +5899,10 @@
         <v>0</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>5496.097296688905</v>
+        <v>5496.097296688907</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>2611.881295037886</v>
+        <v>2611.881295037884</v>
       </c>
       <c r="W79" s="131" t="n">
         <v>2984.036659919334</v>
@@ -5914,7 +5914,7 @@
         <v>0</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>5608.323959220914</v>
+        <v>5608.323959220912</v>
       </c>
     </row>
     <row r="80">
@@ -6015,10 +6015,10 @@
         <v>0</v>
       </c>
       <c r="M81" s="131" t="n">
-        <v>646.2757591213292</v>
+        <v>646.2757591213293</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>669.1214489585097</v>
+        <v>669.1214489585099</v>
       </c>
       <c r="P81" s="130" t="n">
         <v>35.63096672660322</v>
@@ -6045,10 +6045,10 @@
         <v>0</v>
       </c>
       <c r="Y81" s="131" t="n">
-        <v>880.0595490867236</v>
+        <v>880.0595490867238</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>933.776397082107</v>
+        <v>933.7763970821072</v>
       </c>
     </row>
     <row r="82">
@@ -6082,10 +6082,10 @@
         <v>0</v>
       </c>
       <c r="M82" s="134" t="n">
-        <v>646.2757591213292</v>
+        <v>646.2757591213293</v>
       </c>
       <c r="N82" s="135" t="n">
-        <v>646.2757591213292</v>
+        <v>646.2757591213293</v>
       </c>
       <c r="P82" s="133" t="n">
         <v>0</v>
@@ -6112,10 +6112,10 @@
         <v>0</v>
       </c>
       <c r="Y82" s="134" t="n">
-        <v>880.0595490867236</v>
+        <v>880.0595490867238</v>
       </c>
       <c r="Z82" s="135" t="n">
-        <v>880.0595490867236</v>
+        <v>880.0595490867238</v>
       </c>
     </row>
     <row r="83">
@@ -6354,7 +6354,7 @@
         <v>3895.860685324335</v>
       </c>
       <c r="M86" s="143" t="n">
-        <v>647.0252361436105</v>
+        <v>647.0252361436106</v>
       </c>
       <c r="N86" s="144" t="n">
         <v>496534.4141784618</v>
@@ -6384,10 +6384,10 @@
         <v>4038.865980466294</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>880.9559239039352</v>
+        <v>880.9559239039354</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>516784.425697706</v>
+        <v>516784.4256977059</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -6894,7 +6894,7 @@
         <v>0</v>
       </c>
       <c r="Q94" s="131" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="R94" s="131" t="n">
         <v>0</v>
@@ -6903,7 +6903,7 @@
         <v>0</v>
       </c>
       <c r="T94" s="132" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="V94" s="130" t="n">
         <v>0</v>
@@ -6958,7 +6958,7 @@
         <v>26.24432748303783</v>
       </c>
       <c r="P95" s="130" t="n">
-        <v>27.65663487526179</v>
+        <v>27.6566348752618</v>
       </c>
       <c r="Q95" s="131" t="n">
         <v>0</v>
@@ -6967,10 +6967,10 @@
         <v>0</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>1.4464780031783</v>
+        <v>1.446478003178301</v>
       </c>
       <c r="T95" s="132" t="n">
-        <v>29.10311287844009</v>
+        <v>29.1031128784401</v>
       </c>
       <c r="V95" s="130" t="n">
         <v>31.05175440243663</v>
@@ -7040,7 +7040,7 @@
         <v>26.57911917875575</v>
       </c>
       <c r="V96" s="130" t="n">
-        <v>28.06187153348852</v>
+        <v>28.06187153348851</v>
       </c>
       <c r="W96" s="131" t="n">
         <v>0</v>
@@ -7052,7 +7052,7 @@
         <v>0</v>
       </c>
       <c r="Z96" s="132" t="n">
-        <v>28.06187153348852</v>
+        <v>28.06187153348851</v>
       </c>
     </row>
     <row r="97">
@@ -7083,7 +7083,7 @@
         <v>6628.085294105205</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>81.12125915531612</v>
+        <v>81.12125915531614</v>
       </c>
       <c r="M97" s="131" t="n">
         <v>0</v>
@@ -7092,34 +7092,34 @@
         <v>15231.0221184335</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>8787.458946566274</v>
+        <v>8787.458946566276</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>6924.377261876312</v>
       </c>
       <c r="R97" s="131" t="n">
-        <v>85.73780046159801</v>
+        <v>85.73780046159803</v>
       </c>
       <c r="S97" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>15797.57400890418</v>
+        <v>15797.57400890419</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>9058.982559296477</v>
+        <v>9058.982559296473</v>
       </c>
       <c r="W97" s="131" t="n">
         <v>7214.103405258798</v>
       </c>
       <c r="X97" s="131" t="n">
-        <v>90.06841189161894</v>
+        <v>90.06841189161892</v>
       </c>
       <c r="Y97" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>16363.1543764469</v>
+        <v>16363.15437644689</v>
       </c>
     </row>
     <row r="98">
@@ -7159,13 +7159,13 @@
         <v>1051.558057647748</v>
       </c>
       <c r="P98" s="130" t="n">
-        <v>344.8677977438759</v>
+        <v>344.8677977438761</v>
       </c>
       <c r="Q98" s="131" t="n">
-        <v>695.6708181072373</v>
+        <v>695.6708181072372</v>
       </c>
       <c r="R98" s="131" t="n">
-        <v>4.376881306996877</v>
+        <v>4.376881306996878</v>
       </c>
       <c r="S98" s="131" t="n">
         <v>0</v>
@@ -7174,7 +7174,7 @@
         <v>1044.91549715811</v>
       </c>
       <c r="V98" s="130" t="n">
-        <v>337.2252462051626</v>
+        <v>337.2252462051625</v>
       </c>
       <c r="W98" s="131" t="n">
         <v>693.7423997998152</v>
@@ -7220,7 +7220,7 @@
         <v>34.42048685206373</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>4701.938698982582</v>
+        <v>4701.938698982581</v>
       </c>
       <c r="N99" s="132" t="n">
         <v>9591.082297490615</v>
@@ -7235,7 +7235,7 @@
         <v>42.03577551248054</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>5099.728555144815</v>
+        <v>5099.728555144816</v>
       </c>
       <c r="T99" s="132" t="n">
         <v>10943.97587903814</v>
@@ -7302,10 +7302,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>5099.725056957098</v>
+        <v>5099.725056957099</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>5099.725056957098</v>
+        <v>5099.725056957099</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -7492,7 +7492,7 @@
         <v>4086.411781183353</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>552.1088310115438</v>
+        <v>552.1088310115437</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>538270.4316285335</v>
@@ -7507,7 +7507,7 @@
         <v>4115.589524254454</v>
       </c>
       <c r="S103" s="140" t="n">
-        <v>529.4434178862318</v>
+        <v>529.4434178862319</v>
       </c>
       <c r="T103" s="141" t="n">
         <v>541818.6335051483</v>
@@ -7559,7 +7559,7 @@
         <v>4206.317514998797</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>5255.414666079997</v>
+        <v>5255.414666079996</v>
       </c>
       <c r="N104" s="144" t="n">
         <v>568905.4085614788</v>
@@ -7574,7 +7574,7 @@
         <v>4247.739981535529</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>5630.618451034225</v>
+        <v>5630.618451034226</v>
       </c>
       <c r="T104" s="144" t="n">
         <v>574767.6038082013</v>
@@ -7592,7 +7592,7 @@
         <v>6050.69352997534</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>581216.5896308239</v>
+        <v>581216.5896308238</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -8625,10 +8625,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>6296679.872708648</v>
+        <v>6296679.872439795</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>8867.763082677959</v>
+        <v>8867.763082677957</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="AN26" s="58" t="n">
-        <v>7024.58627634705</v>
+        <v>7024.586276347051</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" thickBot="1">
@@ -8779,10 +8779,10 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>634763.5969597775</v>
+        <v>634763.5969597776</v>
       </c>
       <c r="AI27" s="56" t="n">
-        <v>926.3552720223385</v>
+        <v>926.3552720223383</v>
       </c>
       <c r="AK27" s="123" t="n">
         <v>3</v>
@@ -8859,7 +8859,7 @@
         <v>432982.3623017127</v>
       </c>
       <c r="AI28" s="56" t="n">
-        <v>747.2463417280803</v>
+        <v>747.2463417280801</v>
       </c>
       <c r="AK28" s="123" t="n">
         <v>4</v>
@@ -9010,7 +9010,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>195601.2984472009</v>
+        <v>195601.2984393669</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>533.1863182989312</v>
@@ -9144,7 +9144,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>169442.0047022478</v>
+        <v>169442.0044009537</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>1986.350501701309</v>
@@ -9221,7 +9221,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>130915.3156911004</v>
+        <v>130915.3156911005</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>367.4459108674866</v>
@@ -9375,7 +9375,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>122786.8296364548</v>
+        <v>122786.8429110669</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>240.5243126846745</v>
@@ -9532,7 +9532,7 @@
         <v>81509.15863828435</v>
       </c>
       <c r="AI37" s="56" t="n">
-        <v>291.5172533184689</v>
+        <v>291.5172533184688</v>
       </c>
       <c r="AK37" s="123" t="n">
         <v>13</v>
@@ -9736,7 +9736,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>73163.97309959836</v>
+        <v>73163.97307698216</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>201.9551490218655</v>
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>72614.31094965678</v>
+        <v>72614.31094965676</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>147.4175985741262</v>
@@ -9890,7 +9890,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>69138.59455083607</v>
+        <v>69138.59450392729</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>116.7772917320124</v>
@@ -10218,7 +10218,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>6931443.469668426</v>
+        <v>6931443.469399572</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>15281.88969849521</v>
@@ -10234,7 +10234,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>1181805.934094096</v>
+        <v>1181805.934086262</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>7221.299785728896</v>
@@ -10283,7 +10283,7 @@
         <v>432982.3623017127</v>
       </c>
       <c r="AH51" s="56" t="n">
-        <v>832.42410962935</v>
+        <v>832.4241096293499</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" thickBot="1">
@@ -10482,7 +10482,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>308765.5979835189</v>
+        <v>308765.6112380846</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>540.8321250539791</v>
@@ -10563,7 +10563,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>181169.0018992343</v>
+        <v>181169.0015771881</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>2154.971689442402</v>
@@ -10725,7 +10725,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>154220.9816589526</v>
+        <v>154220.981603615</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>415.6609932837869</v>
@@ -10809,7 +10809,7 @@
         <v>141962.3975513979</v>
       </c>
       <c r="AH57" s="56" t="n">
-        <v>514.7302503121009</v>
+        <v>514.7302503121008</v>
       </c>
     </row>
     <row r="58">
@@ -10852,7 +10852,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="R58" s="131" t="n">
         <v>0</v>
@@ -10861,7 +10861,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="V58" s="130" t="n">
         <v>0</v>
@@ -10887,7 +10887,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>104422.0395376931</v>
+        <v>104422.0395065078</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>293.9451907229246</v>
@@ -10930,7 +10930,7 @@
         <v>25.4948504607565</v>
       </c>
       <c r="P59" s="130" t="n">
-        <v>27.65663487526179</v>
+        <v>27.6566348752618</v>
       </c>
       <c r="Q59" s="131" t="n">
         <v>0</v>
@@ -10939,10 +10939,10 @@
         <v>0</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>0.6107794764899804</v>
+        <v>0.6107794764899805</v>
       </c>
       <c r="T59" s="132" t="n">
-        <v>28.26741435175177</v>
+        <v>28.26741435175178</v>
       </c>
       <c r="V59" s="130" t="n">
         <v>31.05175440243663</v>
@@ -10968,10 +10968,10 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>96957.41666861676</v>
+        <v>96957.41662170799</v>
       </c>
       <c r="AH59" s="56" t="n">
-        <v>160.9632940089901</v>
+        <v>160.96329400899</v>
       </c>
     </row>
     <row r="60">
@@ -11011,7 +11011,7 @@
         <v>12.15752497820848</v>
       </c>
       <c r="P60" s="130" t="n">
-        <v>6.618249046619541</v>
+        <v>6.618249046619542</v>
       </c>
       <c r="Q60" s="131" t="n">
         <v>0</v>
@@ -11023,7 +11023,7 @@
         <v>0</v>
       </c>
       <c r="T60" s="132" t="n">
-        <v>6.618249046619541</v>
+        <v>6.618249046619542</v>
       </c>
       <c r="V60" s="130" t="n">
         <v>6.034114128367584</v>
@@ -11052,7 +11052,7 @@
         <v>84557.08086043796</v>
       </c>
       <c r="AH60" s="56" t="n">
-        <v>355.7423952089068</v>
+        <v>355.7423952089067</v>
       </c>
     </row>
     <row r="61">
@@ -11092,13 +11092,13 @@
         <v>9893.16513563129</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>6228.776889941022</v>
+        <v>6228.776889941023</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>3999.114543167052</v>
+        <v>3999.114543167051</v>
       </c>
       <c r="R61" s="131" t="n">
-        <v>73.5852791072068</v>
+        <v>73.58527910720682</v>
       </c>
       <c r="S61" s="131" t="n">
         <v>0</v>
@@ -11107,13 +11107,13 @@
         <v>10301.47671221528</v>
       </c>
       <c r="V61" s="130" t="n">
-        <v>6447.101264258591</v>
+        <v>6447.10126425859</v>
       </c>
       <c r="W61" s="131" t="n">
         <v>4230.066745339464</v>
       </c>
       <c r="X61" s="131" t="n">
-        <v>77.66240762792478</v>
+        <v>77.66240762792476</v>
       </c>
       <c r="Y61" s="131" t="n">
         <v>0</v>
@@ -11133,7 +11133,7 @@
         <v>79633.72037209972</v>
       </c>
       <c r="AH61" s="56" t="n">
-        <v>212.4573984897524</v>
+        <v>212.4573984897525</v>
       </c>
     </row>
     <row r="62">
@@ -11173,13 +11173,13 @@
         <v>1051.558057647748</v>
       </c>
       <c r="P62" s="130" t="n">
-        <v>344.8677977438759</v>
+        <v>344.8677977438761</v>
       </c>
       <c r="Q62" s="131" t="n">
-        <v>695.6708181072373</v>
+        <v>695.6708181072372</v>
       </c>
       <c r="R62" s="131" t="n">
-        <v>4.376881306996877</v>
+        <v>4.376881306996878</v>
       </c>
       <c r="S62" s="131" t="n">
         <v>0</v>
@@ -11188,7 +11188,7 @@
         <v>1044.91549715811</v>
       </c>
       <c r="V62" s="130" t="n">
-        <v>337.2252462051626</v>
+        <v>337.2252462051625</v>
       </c>
       <c r="W62" s="131" t="n">
         <v>693.7423997998152</v>
@@ -11242,7 +11242,7 @@
         <v>2692.467611904198</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>2139.40980991461</v>
+        <v>2139.409809914607</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>34.42048685206299</v>
@@ -11251,22 +11251,22 @@
         <v>4055.662939861252</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>8921.960848532122</v>
+        <v>8921.960848532119</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>3161.62725325569</v>
+        <v>3161.627253255683</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>2604.953328398544</v>
+        <v>2604.953328398546</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>42.03577551248003</v>
+        <v>42.03577551248009</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>4367.592784770583</v>
+        <v>4367.592784770584</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>10176.2091419373</v>
+        <v>10176.20914193729</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>3718.424539440057</v>
@@ -11275,7 +11275,7 @@
         <v>3171.189177178967</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>51.03255827472313</v>
+        <v>51.03255827472316</v>
       </c>
       <c r="Y63" s="131" t="n">
         <v>4661.350612147648</v>
@@ -11344,10 +11344,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>4367.589286582866</v>
+        <v>4367.589286582867</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>4367.589286582866</v>
+        <v>4367.589286582867</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -11569,16 +11569,16 @@
         <v>0</v>
       </c>
       <c r="J67" s="139" t="n">
-        <v>32665.80535718387</v>
+        <v>32665.80535718386</v>
       </c>
       <c r="K67" s="140" t="n">
-        <v>14983.8247713327</v>
+        <v>14983.82477133271</v>
       </c>
       <c r="L67" s="140" t="n">
         <v>202.3739864950116</v>
       </c>
       <c r="M67" s="140" t="n">
-        <v>552.1088310115438</v>
+        <v>552.1088310115437</v>
       </c>
       <c r="N67" s="141" t="n">
         <v>48404.11294602312</v>
@@ -11593,10 +11593,10 @@
         <v>142.2558187419964</v>
       </c>
       <c r="S67" s="140" t="n">
-        <v>529.4434178862318</v>
+        <v>529.4434178862319</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>40480.89080031734</v>
+        <v>40480.89080031735</v>
       </c>
       <c r="V67" s="139" t="n">
         <v>27700.89671012674</v>
@@ -11665,19 +11665,19 @@
         <v>72370.99438301698</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>39238.32152279546</v>
+        <v>39238.32152279547</v>
       </c>
       <c r="Q68" s="143" t="n">
         <v>17647.25318436719</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>262.2537546686801</v>
+        <v>262.2537546686802</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>4897.646982133305</v>
+        <v>4897.646982133306</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>66413.0647305475</v>
+        <v>66413.06473054751</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>38240.73362856136</v>
@@ -12271,10 +12271,10 @@
         <v>0</v>
       </c>
       <c r="M77" s="131" t="n">
-        <v>0.7494770222813295</v>
+        <v>0.7494770222813296</v>
       </c>
       <c r="N77" s="132" t="n">
-        <v>0.7494770222813295</v>
+        <v>0.7494770222813296</v>
       </c>
       <c r="P77" s="130" t="n">
         <v>0</v>
@@ -12286,10 +12286,10 @@
         <v>0</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>0.8356985266883199</v>
+        <v>0.8356985266883201</v>
       </c>
       <c r="T77" s="132" t="n">
-        <v>0.8356985266883199</v>
+        <v>0.8356985266883201</v>
       </c>
       <c r="V77" s="130" t="n">
         <v>0</v>
@@ -12301,10 +12301,10 @@
         <v>0</v>
       </c>
       <c r="Y77" s="131" t="n">
-        <v>0.8963748172115763</v>
+        <v>0.8963748172115764</v>
       </c>
       <c r="Z77" s="132" t="n">
-        <v>0.8963748172115763</v>
+        <v>0.8963748172115764</v>
       </c>
     </row>
     <row r="78">
@@ -12359,7 +12359,7 @@
         <v>19.96087013213621</v>
       </c>
       <c r="V78" s="130" t="n">
-        <v>22.02775740512094</v>
+        <v>22.02775740512093</v>
       </c>
       <c r="W78" s="131" t="n">
         <v>0</v>
@@ -12371,7 +12371,7 @@
         <v>0</v>
       </c>
       <c r="Z78" s="132" t="n">
-        <v>22.02775740512094</v>
+        <v>22.02775740512093</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
@@ -12396,13 +12396,13 @@
         <v>4433</v>
       </c>
       <c r="J79" s="130" t="n">
-        <v>2476.941695579429</v>
+        <v>2476.941695579428</v>
       </c>
       <c r="K79" s="131" t="n">
         <v>2849.092396586792</v>
       </c>
       <c r="L79" s="131" t="n">
-        <v>11.82289063599359</v>
+        <v>11.8228906359936</v>
       </c>
       <c r="M79" s="131" t="n">
         <v>0</v>
@@ -12411,10 +12411,10 @@
         <v>5337.856982802215</v>
       </c>
       <c r="P79" s="130" t="n">
-        <v>2558.682056625252</v>
+        <v>2558.682056625253</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>2925.262718709261</v>
+        <v>2925.262718709262</v>
       </c>
       <c r="R79" s="131" t="n">
         <v>12.15252135439121</v>
@@ -12423,10 +12423,10 @@
         <v>0</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>5496.097296688905</v>
+        <v>5496.097296688907</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>2611.881295037886</v>
+        <v>2611.881295037884</v>
       </c>
       <c r="W79" s="131" t="n">
         <v>2984.036659919334</v>
@@ -12438,7 +12438,7 @@
         <v>0</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>5608.323959220914</v>
+        <v>5608.323959220912</v>
       </c>
     </row>
     <row r="80">
@@ -12539,10 +12539,10 @@
         <v>0</v>
       </c>
       <c r="M81" s="131" t="n">
-        <v>646.2757591213292</v>
+        <v>646.2757591213293</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>669.1214489585097</v>
+        <v>669.1214489585099</v>
       </c>
       <c r="P81" s="130" t="n">
         <v>35.63096672660322</v>
@@ -12569,10 +12569,10 @@
         <v>0</v>
       </c>
       <c r="Y81" s="131" t="n">
-        <v>880.0595490867236</v>
+        <v>880.0595490867238</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>933.776397082107</v>
+        <v>933.7763970821072</v>
       </c>
     </row>
     <row r="82">
@@ -12606,10 +12606,10 @@
         <v>0</v>
       </c>
       <c r="M82" s="134" t="n">
-        <v>646.2757591213292</v>
+        <v>646.2757591213293</v>
       </c>
       <c r="N82" s="135" t="n">
-        <v>646.2757591213292</v>
+        <v>646.2757591213293</v>
       </c>
       <c r="P82" s="133" t="n">
         <v>0</v>
@@ -12636,10 +12636,10 @@
         <v>0</v>
       </c>
       <c r="Y82" s="134" t="n">
-        <v>880.0595490867236</v>
+        <v>880.0595490867238</v>
       </c>
       <c r="Z82" s="135" t="n">
-        <v>880.0595490867236</v>
+        <v>880.0595490867238</v>
       </c>
     </row>
     <row r="83">
@@ -12878,7 +12878,7 @@
         <v>3895.860685324335</v>
       </c>
       <c r="M86" s="143" t="n">
-        <v>647.0252361436105</v>
+        <v>647.0252361436106</v>
       </c>
       <c r="N86" s="144" t="n">
         <v>496534.4141784618</v>
@@ -12908,10 +12908,10 @@
         <v>4038.865980466294</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>880.9559239039352</v>
+        <v>880.9559239039354</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>516784.425697706</v>
+        <v>516784.4256977059</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -13418,7 +13418,7 @@
         <v>0</v>
       </c>
       <c r="Q94" s="131" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="R94" s="131" t="n">
         <v>0</v>
@@ -13427,7 +13427,7 @@
         <v>0</v>
       </c>
       <c r="T94" s="132" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="V94" s="130" t="n">
         <v>0</v>
@@ -13482,7 +13482,7 @@
         <v>26.24432748303783</v>
       </c>
       <c r="P95" s="130" t="n">
-        <v>27.65663487526179</v>
+        <v>27.6566348752618</v>
       </c>
       <c r="Q95" s="131" t="n">
         <v>0</v>
@@ -13491,10 +13491,10 @@
         <v>0</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>1.4464780031783</v>
+        <v>1.446478003178301</v>
       </c>
       <c r="T95" s="132" t="n">
-        <v>29.10311287844009</v>
+        <v>29.1031128784401</v>
       </c>
       <c r="V95" s="130" t="n">
         <v>31.05175440243663</v>
@@ -13564,7 +13564,7 @@
         <v>26.57911917875575</v>
       </c>
       <c r="V96" s="130" t="n">
-        <v>28.06187153348852</v>
+        <v>28.06187153348851</v>
       </c>
       <c r="W96" s="131" t="n">
         <v>0</v>
@@ -13576,7 +13576,7 @@
         <v>0</v>
       </c>
       <c r="Z96" s="132" t="n">
-        <v>28.06187153348852</v>
+        <v>28.06187153348851</v>
       </c>
     </row>
     <row r="97">
@@ -13607,7 +13607,7 @@
         <v>6628.085294105205</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>81.12125915531612</v>
+        <v>81.12125915531614</v>
       </c>
       <c r="M97" s="131" t="n">
         <v>0</v>
@@ -13616,34 +13616,34 @@
         <v>15231.0221184335</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>8787.458946566274</v>
+        <v>8787.458946566276</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>6924.377261876312</v>
       </c>
       <c r="R97" s="131" t="n">
-        <v>85.73780046159801</v>
+        <v>85.73780046159803</v>
       </c>
       <c r="S97" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>15797.57400890418</v>
+        <v>15797.57400890419</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>9058.982559296477</v>
+        <v>9058.982559296473</v>
       </c>
       <c r="W97" s="131" t="n">
         <v>7214.103405258798</v>
       </c>
       <c r="X97" s="131" t="n">
-        <v>90.06841189161894</v>
+        <v>90.06841189161892</v>
       </c>
       <c r="Y97" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>16363.1543764469</v>
+        <v>16363.15437644689</v>
       </c>
     </row>
     <row r="98">
@@ -13683,13 +13683,13 @@
         <v>1051.558057647748</v>
       </c>
       <c r="P98" s="130" t="n">
-        <v>344.8677977438759</v>
+        <v>344.8677977438761</v>
       </c>
       <c r="Q98" s="131" t="n">
-        <v>695.6708181072373</v>
+        <v>695.6708181072372</v>
       </c>
       <c r="R98" s="131" t="n">
-        <v>4.376881306996877</v>
+        <v>4.376881306996878</v>
       </c>
       <c r="S98" s="131" t="n">
         <v>0</v>
@@ -13698,7 +13698,7 @@
         <v>1044.91549715811</v>
       </c>
       <c r="V98" s="130" t="n">
-        <v>337.2252462051626</v>
+        <v>337.2252462051625</v>
       </c>
       <c r="W98" s="131" t="n">
         <v>693.7423997998152</v>
@@ -13744,7 +13744,7 @@
         <v>34.42048685206373</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>4701.938698982582</v>
+        <v>4701.938698982581</v>
       </c>
       <c r="N99" s="132" t="n">
         <v>9591.082297490615</v>
@@ -13759,7 +13759,7 @@
         <v>42.03577551248054</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>5099.728555144815</v>
+        <v>5099.728555144816</v>
       </c>
       <c r="T99" s="132" t="n">
         <v>10943.97587903814</v>
@@ -13826,10 +13826,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>5099.725056957098</v>
+        <v>5099.725056957099</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>5099.725056957098</v>
+        <v>5099.725056957099</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -14016,7 +14016,7 @@
         <v>4086.411781183353</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>552.1088310115438</v>
+        <v>552.1088310115437</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>538270.4316285335</v>
@@ -14031,7 +14031,7 @@
         <v>4115.589524254454</v>
       </c>
       <c r="S103" s="140" t="n">
-        <v>529.4434178862318</v>
+        <v>529.4434178862319</v>
       </c>
       <c r="T103" s="141" t="n">
         <v>541818.6335051483</v>
@@ -14083,7 +14083,7 @@
         <v>4206.317514998797</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>5255.414666079997</v>
+        <v>5255.414666079996</v>
       </c>
       <c r="N104" s="144" t="n">
         <v>568905.4085614788</v>
@@ -14098,7 +14098,7 @@
         <v>4247.739981535529</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>5630.618451034225</v>
+        <v>5630.618451034226</v>
       </c>
       <c r="T104" s="144" t="n">
         <v>574767.6038082013</v>
@@ -14116,7 +14116,7 @@
         <v>6050.69352997534</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>581216.5896308239</v>
+        <v>581216.5896308238</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -15149,7 +15149,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>7800562.638929636</v>
+        <v>7800562.640378885</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>10641.30259354557</v>
@@ -15476,7 +15476,7 @@
         </is>
       </c>
       <c r="AN29" s="58" t="n">
-        <v>896.2858789679237</v>
+        <v>896.2858789679236</v>
       </c>
     </row>
     <row r="30" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -15534,7 +15534,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>215434.4210016179</v>
+        <v>215434.4210419719</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>557.7555438461457</v>
@@ -15597,7 +15597,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>198621.6240102812</v>
+        <v>198621.6259981311</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>2035.572267133469</v>
@@ -15822,7 +15822,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>141528.8650195598</v>
+        <v>141528.8537524001</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>259.2755881015718</v>
@@ -15979,7 +15979,7 @@
         <v>123881.0795628932</v>
       </c>
       <c r="AI36" s="56" t="n">
-        <v>430.1207812819065</v>
+        <v>430.1207812819064</v>
       </c>
       <c r="AK36" s="123" t="n">
         <v>12</v>
@@ -16130,7 +16130,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>84158.24544452075</v>
+        <v>84158.24574711359</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>131.4141574777028</v>
@@ -16193,7 +16193,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>77590.7320794808</v>
+        <v>77590.73220499959</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>199.9598321495294</v>
@@ -16414,7 +16414,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>67285.62852966132</v>
+        <v>67285.62855146721</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>65.9429241414402</v>
@@ -16494,7 +16494,7 @@
         <v>67270.80184550273</v>
       </c>
       <c r="AI43" s="56" t="n">
-        <v>62.16008509289813</v>
+        <v>62.16008509289814</v>
       </c>
       <c r="AK43" s="123" t="n">
         <v>19</v>
@@ -16568,7 +16568,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>63144.63416840847</v>
+        <v>63144.63416840845</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>158.3819594713257</v>
@@ -16742,7 +16742,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>8528904.942646027</v>
+        <v>8528904.944095276</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>17760.98313710272</v>
@@ -16758,7 +16758,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>1210719.956828551</v>
+        <v>1210719.956868905</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>6356.681979750578</v>
@@ -17006,7 +17006,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>354180.0568075458</v>
+        <v>354180.0456662194</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>582.9953975231873</v>
@@ -17087,7 +17087,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>212368.5499542317</v>
+        <v>212368.552079037</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>2208.371887906786</v>
@@ -17249,7 +17249,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>167735.8097736169</v>
+        <v>167735.8100830155</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>411.0858053593449</v>
@@ -17376,7 +17376,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="R58" s="131" t="n">
         <v>0</v>
@@ -17385,7 +17385,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="V58" s="130" t="n">
         <v>0</v>
@@ -17411,7 +17411,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>117275.4374111554</v>
+        <v>117275.4377137483</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>181.1384332800769</v>
@@ -17454,7 +17454,7 @@
         <v>25.4948504607565</v>
       </c>
       <c r="P59" s="130" t="n">
-        <v>27.65663487526179</v>
+        <v>27.6566348752618</v>
       </c>
       <c r="Q59" s="131" t="n">
         <v>0</v>
@@ -17463,10 +17463,10 @@
         <v>0</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>0.6107794764899804</v>
+        <v>0.6107794764899805</v>
       </c>
       <c r="T59" s="132" t="n">
-        <v>28.26741435175177</v>
+        <v>28.26741435175178</v>
       </c>
       <c r="V59" s="130" t="n">
         <v>31.05175440243663</v>
@@ -17535,7 +17535,7 @@
         <v>12.15752497820848</v>
       </c>
       <c r="P60" s="130" t="n">
-        <v>6.618249046619541</v>
+        <v>6.618249046619542</v>
       </c>
       <c r="Q60" s="131" t="n">
         <v>0</v>
@@ -17547,7 +17547,7 @@
         <v>0</v>
       </c>
       <c r="T60" s="132" t="n">
-        <v>6.618249046619541</v>
+        <v>6.618249046619542</v>
       </c>
       <c r="V60" s="130" t="n">
         <v>6.034114128367584</v>
@@ -17573,7 +17573,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>110729.8181819293</v>
+        <v>110729.818355716</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>291.0410122385821</v>
@@ -17616,13 +17616,13 @@
         <v>9893.16513563129</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>6228.776889941022</v>
+        <v>6228.776889941023</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>3999.114543167052</v>
+        <v>3999.114543167051</v>
       </c>
       <c r="R61" s="131" t="n">
-        <v>73.5852791072068</v>
+        <v>73.58527910720682</v>
       </c>
       <c r="S61" s="131" t="n">
         <v>0</v>
@@ -17631,13 +17631,13 @@
         <v>10301.47671221528</v>
       </c>
       <c r="V61" s="130" t="n">
-        <v>6447.101264258591</v>
+        <v>6447.10126425859</v>
       </c>
       <c r="W61" s="131" t="n">
         <v>4230.066745339464</v>
       </c>
       <c r="X61" s="131" t="n">
-        <v>77.66240762792478</v>
+        <v>77.66240762792476</v>
       </c>
       <c r="Y61" s="131" t="n">
         <v>0</v>
@@ -17697,13 +17697,13 @@
         <v>1051.558057647748</v>
       </c>
       <c r="P62" s="130" t="n">
-        <v>344.8677977438759</v>
+        <v>344.8677977438761</v>
       </c>
       <c r="Q62" s="131" t="n">
-        <v>695.6708181072373</v>
+        <v>695.6708181072372</v>
       </c>
       <c r="R62" s="131" t="n">
-        <v>4.376881306996877</v>
+        <v>4.376881306996878</v>
       </c>
       <c r="S62" s="131" t="n">
         <v>0</v>
@@ -17712,7 +17712,7 @@
         <v>1044.91549715811</v>
       </c>
       <c r="V62" s="130" t="n">
-        <v>337.2252462051626</v>
+        <v>337.2252462051625</v>
       </c>
       <c r="W62" s="131" t="n">
         <v>693.7423997998152</v>
@@ -17766,7 +17766,7 @@
         <v>2692.467611904198</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>2139.40980991461</v>
+        <v>2139.409809914607</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>34.42048685206299</v>
@@ -17775,22 +17775,22 @@
         <v>4055.662939861252</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>8921.960848532122</v>
+        <v>8921.960848532119</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>3161.62725325569</v>
+        <v>3161.627253255683</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>2604.953328398544</v>
+        <v>2604.953328398546</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>42.03577551248003</v>
+        <v>42.03577551248009</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>4367.592784770583</v>
+        <v>4367.592784770584</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>10176.2091419373</v>
+        <v>10176.20914193729</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>3718.424539440057</v>
@@ -17799,7 +17799,7 @@
         <v>3171.189177178967</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>51.03255827472313</v>
+        <v>51.03255827472316</v>
       </c>
       <c r="Y63" s="131" t="n">
         <v>4661.350612147648</v>
@@ -17868,10 +17868,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>4367.589286582866</v>
+        <v>4367.589286582867</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>4367.589286582866</v>
+        <v>4367.589286582867</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -18093,16 +18093,16 @@
         <v>0</v>
       </c>
       <c r="J67" s="139" t="n">
-        <v>32665.80535718387</v>
+        <v>32665.80535718386</v>
       </c>
       <c r="K67" s="140" t="n">
-        <v>14983.8247713327</v>
+        <v>14983.82477133271</v>
       </c>
       <c r="L67" s="140" t="n">
         <v>202.3739864950116</v>
       </c>
       <c r="M67" s="140" t="n">
-        <v>552.1088310115438</v>
+        <v>552.1088310115437</v>
       </c>
       <c r="N67" s="141" t="n">
         <v>48404.11294602312</v>
@@ -18117,10 +18117,10 @@
         <v>142.2558187419964</v>
       </c>
       <c r="S67" s="140" t="n">
-        <v>529.4434178862318</v>
+        <v>529.4434178862319</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>40480.89080031734</v>
+        <v>40480.89080031735</v>
       </c>
       <c r="V67" s="139" t="n">
         <v>27700.89671012674</v>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>36553.12059163445</v>
+        <v>36553.1206373299</v>
       </c>
       <c r="AH67" s="56" t="n">
-        <v>63.56123947609334</v>
+        <v>63.56123947609333</v>
       </c>
     </row>
     <row r="68" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -18189,19 +18189,19 @@
         <v>72370.99438301698</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>39238.32152279546</v>
+        <v>39238.32152279547</v>
       </c>
       <c r="Q68" s="143" t="n">
         <v>17647.25318436719</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>262.2537546686801</v>
+        <v>262.2537546686802</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>4897.646982133305</v>
+        <v>4897.646982133306</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>66413.0647305475</v>
+        <v>66413.06473054751</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>38240.73362856136</v>
@@ -18795,10 +18795,10 @@
         <v>0</v>
       </c>
       <c r="M77" s="131" t="n">
-        <v>0.7494770222813295</v>
+        <v>0.7494770222813296</v>
       </c>
       <c r="N77" s="132" t="n">
-        <v>0.7494770222813295</v>
+        <v>0.7494770222813296</v>
       </c>
       <c r="P77" s="130" t="n">
         <v>0</v>
@@ -18810,10 +18810,10 @@
         <v>0</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>0.8356985266883199</v>
+        <v>0.8356985266883201</v>
       </c>
       <c r="T77" s="132" t="n">
-        <v>0.8356985266883199</v>
+        <v>0.8356985266883201</v>
       </c>
       <c r="V77" s="130" t="n">
         <v>0</v>
@@ -18825,10 +18825,10 @@
         <v>0</v>
       </c>
       <c r="Y77" s="131" t="n">
-        <v>0.8963748172115763</v>
+        <v>0.8963748172115764</v>
       </c>
       <c r="Z77" s="132" t="n">
-        <v>0.8963748172115763</v>
+        <v>0.8963748172115764</v>
       </c>
     </row>
     <row r="78">
@@ -18883,7 +18883,7 @@
         <v>19.96087013213621</v>
       </c>
       <c r="V78" s="130" t="n">
-        <v>22.02775740512094</v>
+        <v>22.02775740512093</v>
       </c>
       <c r="W78" s="131" t="n">
         <v>0</v>
@@ -18895,7 +18895,7 @@
         <v>0</v>
       </c>
       <c r="Z78" s="132" t="n">
-        <v>22.02775740512094</v>
+        <v>22.02775740512093</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
@@ -18920,13 +18920,13 @@
         <v>4433</v>
       </c>
       <c r="J79" s="130" t="n">
-        <v>2476.941695579429</v>
+        <v>2476.941695579428</v>
       </c>
       <c r="K79" s="131" t="n">
         <v>2849.092396586792</v>
       </c>
       <c r="L79" s="131" t="n">
-        <v>11.82289063599359</v>
+        <v>11.8228906359936</v>
       </c>
       <c r="M79" s="131" t="n">
         <v>0</v>
@@ -18935,10 +18935,10 @@
         <v>5337.856982802215</v>
       </c>
       <c r="P79" s="130" t="n">
-        <v>2558.682056625252</v>
+        <v>2558.682056625253</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>2925.262718709261</v>
+        <v>2925.262718709262</v>
       </c>
       <c r="R79" s="131" t="n">
         <v>12.15252135439121</v>
@@ -18947,10 +18947,10 @@
         <v>0</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>5496.097296688905</v>
+        <v>5496.097296688907</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>2611.881295037886</v>
+        <v>2611.881295037884</v>
       </c>
       <c r="W79" s="131" t="n">
         <v>2984.036659919334</v>
@@ -18962,7 +18962,7 @@
         <v>0</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>5608.323959220914</v>
+        <v>5608.323959220912</v>
       </c>
     </row>
     <row r="80">
@@ -19063,10 +19063,10 @@
         <v>0</v>
       </c>
       <c r="M81" s="131" t="n">
-        <v>646.2757591213292</v>
+        <v>646.2757591213293</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>669.1214489585097</v>
+        <v>669.1214489585099</v>
       </c>
       <c r="P81" s="130" t="n">
         <v>35.63096672660322</v>
@@ -19093,10 +19093,10 @@
         <v>0</v>
       </c>
       <c r="Y81" s="131" t="n">
-        <v>880.0595490867236</v>
+        <v>880.0595490867238</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>933.776397082107</v>
+        <v>933.7763970821072</v>
       </c>
     </row>
     <row r="82">
@@ -19130,10 +19130,10 @@
         <v>0</v>
       </c>
       <c r="M82" s="134" t="n">
-        <v>646.2757591213292</v>
+        <v>646.2757591213293</v>
       </c>
       <c r="N82" s="135" t="n">
-        <v>646.2757591213292</v>
+        <v>646.2757591213293</v>
       </c>
       <c r="P82" s="133" t="n">
         <v>0</v>
@@ -19160,10 +19160,10 @@
         <v>0</v>
       </c>
       <c r="Y82" s="134" t="n">
-        <v>880.0595490867236</v>
+        <v>880.0595490867238</v>
       </c>
       <c r="Z82" s="135" t="n">
-        <v>880.0595490867236</v>
+        <v>880.0595490867238</v>
       </c>
     </row>
     <row r="83">
@@ -19402,7 +19402,7 @@
         <v>3895.860685324335</v>
       </c>
       <c r="M86" s="143" t="n">
-        <v>647.0252361436105</v>
+        <v>647.0252361436106</v>
       </c>
       <c r="N86" s="144" t="n">
         <v>496534.4141784618</v>
@@ -19432,10 +19432,10 @@
         <v>4038.865980466294</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>880.9559239039352</v>
+        <v>880.9559239039354</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>516784.425697706</v>
+        <v>516784.4256977059</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -19942,7 +19942,7 @@
         <v>0</v>
       </c>
       <c r="Q94" s="131" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="R94" s="131" t="n">
         <v>0</v>
@@ -19951,7 +19951,7 @@
         <v>0</v>
       </c>
       <c r="T94" s="132" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="V94" s="130" t="n">
         <v>0</v>
@@ -20006,7 +20006,7 @@
         <v>26.24432748303783</v>
       </c>
       <c r="P95" s="130" t="n">
-        <v>27.65663487526179</v>
+        <v>27.6566348752618</v>
       </c>
       <c r="Q95" s="131" t="n">
         <v>0</v>
@@ -20015,10 +20015,10 @@
         <v>0</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>1.4464780031783</v>
+        <v>1.446478003178301</v>
       </c>
       <c r="T95" s="132" t="n">
-        <v>29.10311287844009</v>
+        <v>29.1031128784401</v>
       </c>
       <c r="V95" s="130" t="n">
         <v>31.05175440243663</v>
@@ -20088,7 +20088,7 @@
         <v>26.57911917875575</v>
       </c>
       <c r="V96" s="130" t="n">
-        <v>28.06187153348852</v>
+        <v>28.06187153348851</v>
       </c>
       <c r="W96" s="131" t="n">
         <v>0</v>
@@ -20100,7 +20100,7 @@
         <v>0</v>
       </c>
       <c r="Z96" s="132" t="n">
-        <v>28.06187153348852</v>
+        <v>28.06187153348851</v>
       </c>
     </row>
     <row r="97">
@@ -20131,7 +20131,7 @@
         <v>6628.085294105205</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>81.12125915531612</v>
+        <v>81.12125915531614</v>
       </c>
       <c r="M97" s="131" t="n">
         <v>0</v>
@@ -20140,34 +20140,34 @@
         <v>15231.0221184335</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>8787.458946566274</v>
+        <v>8787.458946566276</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>6924.377261876312</v>
       </c>
       <c r="R97" s="131" t="n">
-        <v>85.73780046159801</v>
+        <v>85.73780046159803</v>
       </c>
       <c r="S97" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>15797.57400890418</v>
+        <v>15797.57400890419</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>9058.982559296477</v>
+        <v>9058.982559296473</v>
       </c>
       <c r="W97" s="131" t="n">
         <v>7214.103405258798</v>
       </c>
       <c r="X97" s="131" t="n">
-        <v>90.06841189161894</v>
+        <v>90.06841189161892</v>
       </c>
       <c r="Y97" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>16363.1543764469</v>
+        <v>16363.15437644689</v>
       </c>
     </row>
     <row r="98">
@@ -20207,13 +20207,13 @@
         <v>1051.558057647748</v>
       </c>
       <c r="P98" s="130" t="n">
-        <v>344.8677977438759</v>
+        <v>344.8677977438761</v>
       </c>
       <c r="Q98" s="131" t="n">
-        <v>695.6708181072373</v>
+        <v>695.6708181072372</v>
       </c>
       <c r="R98" s="131" t="n">
-        <v>4.376881306996877</v>
+        <v>4.376881306996878</v>
       </c>
       <c r="S98" s="131" t="n">
         <v>0</v>
@@ -20222,7 +20222,7 @@
         <v>1044.91549715811</v>
       </c>
       <c r="V98" s="130" t="n">
-        <v>337.2252462051626</v>
+        <v>337.2252462051625</v>
       </c>
       <c r="W98" s="131" t="n">
         <v>693.7423997998152</v>
@@ -20268,7 +20268,7 @@
         <v>34.42048685206373</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>4701.938698982582</v>
+        <v>4701.938698982581</v>
       </c>
       <c r="N99" s="132" t="n">
         <v>9591.082297490615</v>
@@ -20283,7 +20283,7 @@
         <v>42.03577551248054</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>5099.728555144815</v>
+        <v>5099.728555144816</v>
       </c>
       <c r="T99" s="132" t="n">
         <v>10943.97587903814</v>
@@ -20350,10 +20350,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>5099.725056957098</v>
+        <v>5099.725056957099</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>5099.725056957098</v>
+        <v>5099.725056957099</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -20540,7 +20540,7 @@
         <v>4086.411781183353</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>552.1088310115438</v>
+        <v>552.1088310115437</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>538270.4316285335</v>
@@ -20555,7 +20555,7 @@
         <v>4115.589524254454</v>
       </c>
       <c r="S103" s="140" t="n">
-        <v>529.4434178862318</v>
+        <v>529.4434178862319</v>
       </c>
       <c r="T103" s="141" t="n">
         <v>541818.6335051483</v>
@@ -20607,7 +20607,7 @@
         <v>4206.317514998797</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>5255.414666079997</v>
+        <v>5255.414666079996</v>
       </c>
       <c r="N104" s="144" t="n">
         <v>568905.4085614788</v>
@@ -20622,7 +20622,7 @@
         <v>4247.739981535529</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>5630.618451034225</v>
+        <v>5630.618451034226</v>
       </c>
       <c r="T104" s="144" t="n">
         <v>574767.6038082013</v>
@@ -20640,7 +20640,7 @@
         <v>6050.69352997534</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>581216.5896308239</v>
+        <v>581216.5896308238</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -21673,7 +21673,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>9597999.980747234</v>
+        <v>9597999.977926435</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>12769.54856496323</v>
@@ -21827,7 +21827,7 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>828266.6217095609</v>
+        <v>828266.6217095607</v>
       </c>
       <c r="AI27" s="56" t="n">
         <v>1141.362330658724</v>
@@ -21904,7 +21904,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>467965.6858161184</v>
+        <v>467965.6858161185</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>745.1977318077994</v>
@@ -21981,7 +21981,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>250680.0442883839</v>
+        <v>250680.0442883838</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>218.3281904331627</v>
@@ -22058,7 +22058,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>234494.3511181713</v>
+        <v>234494.3510725113</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>583.4569193065761</v>
@@ -22192,7 +22192,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>161088.4431730375</v>
+        <v>161088.4549432689</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>278.4775381563741</v>
@@ -22269,10 +22269,10 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>152313.343536535</v>
+        <v>152313.3435365351</v>
       </c>
       <c r="AI33" s="56" t="n">
-        <v>386.0779912577576</v>
+        <v>386.0779912577577</v>
       </c>
       <c r="AK33" s="123" t="n">
         <v>9</v>
@@ -22654,7 +22654,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>100514.8991294782</v>
+        <v>100514.8986135323</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>147.4348574158096</v>
@@ -22717,7 +22717,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>81399.4248451857</v>
+        <v>81399.42466296813</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>197.9842290078921</v>
@@ -22784,7 +22784,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>76209.36499506667</v>
+        <v>76209.36496274141</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>70.82665710335527</v>
@@ -23015,7 +23015,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>62054.60764247372</v>
+        <v>62054.60747581825</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>62.77817334161035</v>
@@ -23266,7 +23266,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>10426266.6024568</v>
+        <v>10426266.599636</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>20672.39396831167</v>
@@ -23282,7 +23282,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>1268825.844083462</v>
+        <v>1268825.844037802</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>6395.928872955813</v>
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>467965.6858161184</v>
+        <v>467965.6858161185</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>767.6697553968106</v>
@@ -23449,7 +23449,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>400752.3106225545</v>
+        <v>400752.3221938051</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>626.1720366637545</v>
@@ -23611,7 +23611,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>180608.7984159936</v>
+        <v>180608.7979594305</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>416.1816363077455</v>
@@ -23900,7 +23900,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="R58" s="131" t="n">
         <v>0</v>
@@ -23909,7 +23909,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="V58" s="130" t="n">
         <v>0</v>
@@ -23935,7 +23935,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>139381.0259237133</v>
+        <v>139381.0254077674</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>203.221019681251</v>
@@ -23978,7 +23978,7 @@
         <v>25.4948504607565</v>
       </c>
       <c r="P59" s="130" t="n">
-        <v>27.65663487526179</v>
+        <v>27.6566348752618</v>
       </c>
       <c r="Q59" s="131" t="n">
         <v>0</v>
@@ -23987,10 +23987,10 @@
         <v>0</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>0.6107794764899804</v>
+        <v>0.6107794764899805</v>
       </c>
       <c r="T59" s="132" t="n">
-        <v>28.26741435175177</v>
+        <v>28.26741435175178</v>
       </c>
       <c r="V59" s="130" t="n">
         <v>31.05175440243663</v>
@@ -24016,7 +24016,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>116137.4179914892</v>
+        <v>116137.417737935</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>288.1655270376649</v>
@@ -24059,7 +24059,7 @@
         <v>12.15752497820848</v>
       </c>
       <c r="P60" s="130" t="n">
-        <v>6.618249046619541</v>
+        <v>6.618249046619542</v>
       </c>
       <c r="Q60" s="131" t="n">
         <v>0</v>
@@ -24071,7 +24071,7 @@
         <v>0</v>
       </c>
       <c r="T60" s="132" t="n">
-        <v>6.618249046619541</v>
+        <v>6.618249046619542</v>
       </c>
       <c r="V60" s="130" t="n">
         <v>6.034114128367584</v>
@@ -24097,7 +24097,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>59901.00586583805</v>
+        <v>59901.00586583806</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>140.1553635753655</v>
@@ -24140,13 +24140,13 @@
         <v>9893.16513563129</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>6228.776889941022</v>
+        <v>6228.776889941023</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>3999.114543167052</v>
+        <v>3999.114543167051</v>
       </c>
       <c r="R61" s="131" t="n">
-        <v>73.5852791072068</v>
+        <v>73.58527910720682</v>
       </c>
       <c r="S61" s="131" t="n">
         <v>0</v>
@@ -24155,13 +24155,13 @@
         <v>10301.47671221528</v>
       </c>
       <c r="V61" s="130" t="n">
-        <v>6447.101264258591</v>
+        <v>6447.10126425859</v>
       </c>
       <c r="W61" s="131" t="n">
         <v>4230.066745339464</v>
       </c>
       <c r="X61" s="131" t="n">
-        <v>77.66240762792478</v>
+        <v>77.66240762792476</v>
       </c>
       <c r="Y61" s="131" t="n">
         <v>0</v>
@@ -24221,13 +24221,13 @@
         <v>1051.558057647748</v>
       </c>
       <c r="P62" s="130" t="n">
-        <v>344.8677977438759</v>
+        <v>344.8677977438761</v>
       </c>
       <c r="Q62" s="131" t="n">
-        <v>695.6708181072373</v>
+        <v>695.6708181072372</v>
       </c>
       <c r="R62" s="131" t="n">
-        <v>4.376881306996877</v>
+        <v>4.376881306996878</v>
       </c>
       <c r="S62" s="131" t="n">
         <v>0</v>
@@ -24236,7 +24236,7 @@
         <v>1044.91549715811</v>
       </c>
       <c r="V62" s="130" t="n">
-        <v>337.2252462051626</v>
+        <v>337.2252462051625</v>
       </c>
       <c r="W62" s="131" t="n">
         <v>693.7423997998152</v>
@@ -24290,7 +24290,7 @@
         <v>2692.467611904198</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>2139.40980991461</v>
+        <v>2139.409809914607</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>34.42048685206299</v>
@@ -24299,22 +24299,22 @@
         <v>4055.662939861252</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>8921.960848532122</v>
+        <v>8921.960848532119</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>3161.62725325569</v>
+        <v>3161.627253255683</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>2604.953328398544</v>
+        <v>2604.953328398546</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>42.03577551248003</v>
+        <v>42.03577551248009</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>4367.592784770583</v>
+        <v>4367.592784770584</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>10176.2091419373</v>
+        <v>10176.20914193729</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>3718.424539440057</v>
@@ -24323,7 +24323,7 @@
         <v>3171.189177178967</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>51.03255827472313</v>
+        <v>51.03255827472316</v>
       </c>
       <c r="Y63" s="131" t="n">
         <v>4661.350612147648</v>
@@ -24392,10 +24392,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>4367.589286582866</v>
+        <v>4367.589286582867</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>4367.589286582866</v>
+        <v>4367.589286582867</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -24507,7 +24507,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>35380.24344812193</v>
+        <v>35380.24338444939</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>57.89489579250349</v>
@@ -24592,7 +24592,7 @@
         <v>34478.21295394358</v>
       </c>
       <c r="AH66" s="56" t="n">
-        <v>178.3718972954333</v>
+        <v>178.3718972954334</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" thickBot="1">
@@ -24617,16 +24617,16 @@
         <v>0</v>
       </c>
       <c r="J67" s="139" t="n">
-        <v>32665.80535718387</v>
+        <v>32665.80535718386</v>
       </c>
       <c r="K67" s="140" t="n">
-        <v>14983.8247713327</v>
+        <v>14983.82477133271</v>
       </c>
       <c r="L67" s="140" t="n">
         <v>202.3739864950116</v>
       </c>
       <c r="M67" s="140" t="n">
-        <v>552.1088310115438</v>
+        <v>552.1088310115437</v>
       </c>
       <c r="N67" s="141" t="n">
         <v>48404.11294602312</v>
@@ -24641,10 +24641,10 @@
         <v>142.2558187419964</v>
       </c>
       <c r="S67" s="140" t="n">
-        <v>529.4434178862318</v>
+        <v>529.4434178862319</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>40480.89080031734</v>
+        <v>40480.89080031735</v>
       </c>
       <c r="V67" s="139" t="n">
         <v>27700.89671012674</v>
@@ -24713,19 +24713,19 @@
         <v>72370.99438301698</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>39238.32152279546</v>
+        <v>39238.32152279547</v>
       </c>
       <c r="Q68" s="143" t="n">
         <v>17647.25318436719</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>262.2537546686801</v>
+        <v>262.2537546686802</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>4897.646982133305</v>
+        <v>4897.646982133306</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>66413.0647305475</v>
+        <v>66413.06473054751</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>38240.73362856136</v>
@@ -25319,10 +25319,10 @@
         <v>0</v>
       </c>
       <c r="M77" s="131" t="n">
-        <v>0.7494770222813295</v>
+        <v>0.7494770222813296</v>
       </c>
       <c r="N77" s="132" t="n">
-        <v>0.7494770222813295</v>
+        <v>0.7494770222813296</v>
       </c>
       <c r="P77" s="130" t="n">
         <v>0</v>
@@ -25334,10 +25334,10 @@
         <v>0</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>0.8356985266883199</v>
+        <v>0.8356985266883201</v>
       </c>
       <c r="T77" s="132" t="n">
-        <v>0.8356985266883199</v>
+        <v>0.8356985266883201</v>
       </c>
       <c r="V77" s="130" t="n">
         <v>0</v>
@@ -25349,10 +25349,10 @@
         <v>0</v>
       </c>
       <c r="Y77" s="131" t="n">
-        <v>0.8963748172115763</v>
+        <v>0.8963748172115764</v>
       </c>
       <c r="Z77" s="132" t="n">
-        <v>0.8963748172115763</v>
+        <v>0.8963748172115764</v>
       </c>
     </row>
     <row r="78">
@@ -25407,7 +25407,7 @@
         <v>19.96087013213621</v>
       </c>
       <c r="V78" s="130" t="n">
-        <v>22.02775740512094</v>
+        <v>22.02775740512093</v>
       </c>
       <c r="W78" s="131" t="n">
         <v>0</v>
@@ -25419,7 +25419,7 @@
         <v>0</v>
       </c>
       <c r="Z78" s="132" t="n">
-        <v>22.02775740512094</v>
+        <v>22.02775740512093</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
@@ -25444,13 +25444,13 @@
         <v>4433</v>
       </c>
       <c r="J79" s="130" t="n">
-        <v>2476.941695579429</v>
+        <v>2476.941695579428</v>
       </c>
       <c r="K79" s="131" t="n">
         <v>2849.092396586792</v>
       </c>
       <c r="L79" s="131" t="n">
-        <v>11.82289063599359</v>
+        <v>11.8228906359936</v>
       </c>
       <c r="M79" s="131" t="n">
         <v>0</v>
@@ -25459,10 +25459,10 @@
         <v>5337.856982802215</v>
       </c>
       <c r="P79" s="130" t="n">
-        <v>2558.682056625252</v>
+        <v>2558.682056625253</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>2925.262718709261</v>
+        <v>2925.262718709262</v>
       </c>
       <c r="R79" s="131" t="n">
         <v>12.15252135439121</v>
@@ -25471,10 +25471,10 @@
         <v>0</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>5496.097296688905</v>
+        <v>5496.097296688907</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>2611.881295037886</v>
+        <v>2611.881295037884</v>
       </c>
       <c r="W79" s="131" t="n">
         <v>2984.036659919334</v>
@@ -25486,7 +25486,7 @@
         <v>0</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>5608.323959220914</v>
+        <v>5608.323959220912</v>
       </c>
     </row>
     <row r="80">
@@ -25587,10 +25587,10 @@
         <v>0</v>
       </c>
       <c r="M81" s="131" t="n">
-        <v>646.2757591213292</v>
+        <v>646.2757591213293</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>669.1214489585097</v>
+        <v>669.1214489585099</v>
       </c>
       <c r="P81" s="130" t="n">
         <v>35.63096672660322</v>
@@ -25617,10 +25617,10 @@
         <v>0</v>
       </c>
       <c r="Y81" s="131" t="n">
-        <v>880.0595490867236</v>
+        <v>880.0595490867238</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>933.776397082107</v>
+        <v>933.7763970821072</v>
       </c>
     </row>
     <row r="82">
@@ -25654,10 +25654,10 @@
         <v>0</v>
       </c>
       <c r="M82" s="134" t="n">
-        <v>646.2757591213292</v>
+        <v>646.2757591213293</v>
       </c>
       <c r="N82" s="135" t="n">
-        <v>646.2757591213292</v>
+        <v>646.2757591213293</v>
       </c>
       <c r="P82" s="133" t="n">
         <v>0</v>
@@ -25684,10 +25684,10 @@
         <v>0</v>
       </c>
       <c r="Y82" s="134" t="n">
-        <v>880.0595490867236</v>
+        <v>880.0595490867238</v>
       </c>
       <c r="Z82" s="135" t="n">
-        <v>880.0595490867236</v>
+        <v>880.0595490867238</v>
       </c>
     </row>
     <row r="83">
@@ -25926,7 +25926,7 @@
         <v>3895.860685324335</v>
       </c>
       <c r="M86" s="143" t="n">
-        <v>647.0252361436105</v>
+        <v>647.0252361436106</v>
       </c>
       <c r="N86" s="144" t="n">
         <v>496534.4141784618</v>
@@ -25956,10 +25956,10 @@
         <v>4038.865980466294</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>880.9559239039352</v>
+        <v>880.9559239039354</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>516784.425697706</v>
+        <v>516784.4256977059</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -26466,7 +26466,7 @@
         <v>0</v>
       </c>
       <c r="Q94" s="131" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="R94" s="131" t="n">
         <v>0</v>
@@ -26475,7 +26475,7 @@
         <v>0</v>
       </c>
       <c r="T94" s="132" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="V94" s="130" t="n">
         <v>0</v>
@@ -26530,7 +26530,7 @@
         <v>26.24432748303783</v>
       </c>
       <c r="P95" s="130" t="n">
-        <v>27.65663487526179</v>
+        <v>27.6566348752618</v>
       </c>
       <c r="Q95" s="131" t="n">
         <v>0</v>
@@ -26539,10 +26539,10 @@
         <v>0</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>1.4464780031783</v>
+        <v>1.446478003178301</v>
       </c>
       <c r="T95" s="132" t="n">
-        <v>29.10311287844009</v>
+        <v>29.1031128784401</v>
       </c>
       <c r="V95" s="130" t="n">
         <v>31.05175440243663</v>
@@ -26612,7 +26612,7 @@
         <v>26.57911917875575</v>
       </c>
       <c r="V96" s="130" t="n">
-        <v>28.06187153348852</v>
+        <v>28.06187153348851</v>
       </c>
       <c r="W96" s="131" t="n">
         <v>0</v>
@@ -26624,7 +26624,7 @@
         <v>0</v>
       </c>
       <c r="Z96" s="132" t="n">
-        <v>28.06187153348852</v>
+        <v>28.06187153348851</v>
       </c>
     </row>
     <row r="97">
@@ -26655,7 +26655,7 @@
         <v>6628.085294105205</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>81.12125915531612</v>
+        <v>81.12125915531614</v>
       </c>
       <c r="M97" s="131" t="n">
         <v>0</v>
@@ -26664,34 +26664,34 @@
         <v>15231.0221184335</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>8787.458946566274</v>
+        <v>8787.458946566276</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>6924.377261876312</v>
       </c>
       <c r="R97" s="131" t="n">
-        <v>85.73780046159801</v>
+        <v>85.73780046159803</v>
       </c>
       <c r="S97" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>15797.57400890418</v>
+        <v>15797.57400890419</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>9058.982559296477</v>
+        <v>9058.982559296473</v>
       </c>
       <c r="W97" s="131" t="n">
         <v>7214.103405258798</v>
       </c>
       <c r="X97" s="131" t="n">
-        <v>90.06841189161894</v>
+        <v>90.06841189161892</v>
       </c>
       <c r="Y97" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>16363.1543764469</v>
+        <v>16363.15437644689</v>
       </c>
     </row>
     <row r="98">
@@ -26731,13 +26731,13 @@
         <v>1051.558057647748</v>
       </c>
       <c r="P98" s="130" t="n">
-        <v>344.8677977438759</v>
+        <v>344.8677977438761</v>
       </c>
       <c r="Q98" s="131" t="n">
-        <v>695.6708181072373</v>
+        <v>695.6708181072372</v>
       </c>
       <c r="R98" s="131" t="n">
-        <v>4.376881306996877</v>
+        <v>4.376881306996878</v>
       </c>
       <c r="S98" s="131" t="n">
         <v>0</v>
@@ -26746,7 +26746,7 @@
         <v>1044.91549715811</v>
       </c>
       <c r="V98" s="130" t="n">
-        <v>337.2252462051626</v>
+        <v>337.2252462051625</v>
       </c>
       <c r="W98" s="131" t="n">
         <v>693.7423997998152</v>
@@ -26792,7 +26792,7 @@
         <v>34.42048685206373</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>4701.938698982582</v>
+        <v>4701.938698982581</v>
       </c>
       <c r="N99" s="132" t="n">
         <v>9591.082297490615</v>
@@ -26807,7 +26807,7 @@
         <v>42.03577551248054</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>5099.728555144815</v>
+        <v>5099.728555144816</v>
       </c>
       <c r="T99" s="132" t="n">
         <v>10943.97587903814</v>
@@ -26874,10 +26874,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>5099.725056957098</v>
+        <v>5099.725056957099</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>5099.725056957098</v>
+        <v>5099.725056957099</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -27064,7 +27064,7 @@
         <v>4086.411781183353</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>552.1088310115438</v>
+        <v>552.1088310115437</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>538270.4316285335</v>
@@ -27079,7 +27079,7 @@
         <v>4115.589524254454</v>
       </c>
       <c r="S103" s="140" t="n">
-        <v>529.4434178862318</v>
+        <v>529.4434178862319</v>
       </c>
       <c r="T103" s="141" t="n">
         <v>541818.6335051483</v>
@@ -27131,7 +27131,7 @@
         <v>4206.317514998797</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>5255.414666079997</v>
+        <v>5255.414666079996</v>
       </c>
       <c r="N104" s="144" t="n">
         <v>568905.4085614788</v>
@@ -27146,7 +27146,7 @@
         <v>4247.739981535529</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>5630.618451034225</v>
+        <v>5630.618451034226</v>
       </c>
       <c r="T104" s="144" t="n">
         <v>574767.6038082013</v>
@@ -27164,7 +27164,7 @@
         <v>6050.69352997534</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>581216.5896308239</v>
+        <v>581216.5896308238</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -28197,7 +28197,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>11954844.09441201</v>
+        <v>11954844.10030087</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>15323.44213046236</v>
@@ -28582,7 +28582,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>184743.6108732122</v>
+        <v>184743.598825857</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>299.1015846322352</v>
@@ -28648,7 +28648,7 @@
         <v>159886.4982688307</v>
       </c>
       <c r="AI31" s="56" t="n">
-        <v>50.88335227286235</v>
+        <v>50.88335227286236</v>
       </c>
       <c r="AK31" s="123" t="n">
         <v>7</v>
@@ -28735,7 +28735,7 @@
         </is>
       </c>
       <c r="AN32" s="58" t="n">
-        <v>36.82479549314452</v>
+        <v>36.82479549314451</v>
       </c>
     </row>
     <row r="33">
@@ -28796,7 +28796,7 @@
         <v>132144.4016893462</v>
       </c>
       <c r="AI33" s="56" t="n">
-        <v>423.4029250633001</v>
+        <v>423.4029250633002</v>
       </c>
       <c r="AK33" s="123" t="n">
         <v>9</v>
@@ -28870,7 +28870,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>121104.1172550125</v>
+        <v>121104.1180196402</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>165.4086408833709</v>
@@ -29024,7 +29024,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>87232.73634244142</v>
+        <v>87232.73638597791</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>76.07207932842975</v>
@@ -29101,7 +29101,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>86239.43611018968</v>
+        <v>86239.43634990924</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>196.0281448252941</v>
@@ -29178,7 +29178,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>72238.9904084279</v>
+        <v>72238.99042074624</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>247.7889289672761</v>
@@ -29241,7 +29241,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>71891.09061715334</v>
+        <v>71891.09086100316</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>67.42752485929</v>
@@ -29616,7 +29616,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>48816.44477828774</v>
+        <v>48816.44477828775</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>164.2623045529861</v>
@@ -29790,7 +29790,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>12906800.87633019</v>
+        <v>12906800.88221905</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>24095.60052817913</v>
@@ -29806,7 +29806,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>1007460.798091039</v>
+        <v>1007460.798103358</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>4257.422574251343</v>
@@ -29973,7 +29973,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>457700.9808550433</v>
+        <v>457700.9690950744</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>672.5463376990722</v>
@@ -30138,7 +30138,7 @@
         <v>241053.7570896112</v>
       </c>
       <c r="AH54" s="56" t="n">
-        <v>582.9831014558807</v>
+        <v>582.9831014558808</v>
       </c>
     </row>
     <row r="55">
@@ -30378,7 +30378,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>123014.8854264333</v>
+        <v>123014.8857602784</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>285.3184516305328</v>
@@ -30424,7 +30424,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="R58" s="131" t="n">
         <v>0</v>
@@ -30433,7 +30433,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="V58" s="130" t="n">
         <v>0</v>
@@ -30459,7 +30459,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>121104.1172550125</v>
+        <v>121104.1180196402</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>178.5021877230272</v>
@@ -30502,7 +30502,7 @@
         <v>25.4948504607565</v>
       </c>
       <c r="P59" s="130" t="n">
-        <v>27.65663487526179</v>
+        <v>27.6566348752618</v>
       </c>
       <c r="Q59" s="131" t="n">
         <v>0</v>
@@ -30511,10 +30511,10 @@
         <v>0</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>0.6107794764899804</v>
+        <v>0.6107794764899805</v>
       </c>
       <c r="T59" s="132" t="n">
-        <v>28.26741435175177</v>
+        <v>28.26741435175178</v>
       </c>
       <c r="V59" s="130" t="n">
         <v>31.05175440243663</v>
@@ -30540,7 +30540,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>79997.16163236521</v>
+        <v>79997.16224496395</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>195.1197448750256</v>
@@ -30583,7 +30583,7 @@
         <v>12.15752497820848</v>
       </c>
       <c r="P60" s="130" t="n">
-        <v>6.618249046619541</v>
+        <v>6.618249046619542</v>
       </c>
       <c r="Q60" s="131" t="n">
         <v>0</v>
@@ -30595,7 +30595,7 @@
         <v>0</v>
       </c>
       <c r="T60" s="132" t="n">
-        <v>6.618249046619541</v>
+        <v>6.618249046619542</v>
       </c>
       <c r="V60" s="130" t="n">
         <v>6.034114128367584</v>
@@ -30664,13 +30664,13 @@
         <v>9893.16513563129</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>6228.776889941022</v>
+        <v>6228.776889941023</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>3999.114543167052</v>
+        <v>3999.114543167051</v>
       </c>
       <c r="R61" s="131" t="n">
-        <v>73.5852791072068</v>
+        <v>73.58527910720682</v>
       </c>
       <c r="S61" s="131" t="n">
         <v>0</v>
@@ -30679,13 +30679,13 @@
         <v>10301.47671221528</v>
       </c>
       <c r="V61" s="130" t="n">
-        <v>6447.101264258591</v>
+        <v>6447.10126425859</v>
       </c>
       <c r="W61" s="131" t="n">
         <v>4230.066745339464</v>
       </c>
       <c r="X61" s="131" t="n">
-        <v>77.66240762792478</v>
+        <v>77.66240762792476</v>
       </c>
       <c r="Y61" s="131" t="n">
         <v>0</v>
@@ -30745,13 +30745,13 @@
         <v>1051.558057647748</v>
       </c>
       <c r="P62" s="130" t="n">
-        <v>344.8677977438759</v>
+        <v>344.8677977438761</v>
       </c>
       <c r="Q62" s="131" t="n">
-        <v>695.6708181072373</v>
+        <v>695.6708181072372</v>
       </c>
       <c r="R62" s="131" t="n">
-        <v>4.376881306996877</v>
+        <v>4.376881306996878</v>
       </c>
       <c r="S62" s="131" t="n">
         <v>0</v>
@@ -30760,7 +30760,7 @@
         <v>1044.91549715811</v>
       </c>
       <c r="V62" s="130" t="n">
-        <v>337.2252462051626</v>
+        <v>337.2252462051625</v>
       </c>
       <c r="W62" s="131" t="n">
         <v>693.7423997998152</v>
@@ -30814,7 +30814,7 @@
         <v>2692.467611904198</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>2139.40980991461</v>
+        <v>2139.409809914607</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>34.42048685206299</v>
@@ -30823,22 +30823,22 @@
         <v>4055.662939861252</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>8921.960848532122</v>
+        <v>8921.960848532119</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>3161.62725325569</v>
+        <v>3161.627253255683</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>2604.953328398544</v>
+        <v>2604.953328398546</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>42.03577551248003</v>
+        <v>42.03577551248009</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>4367.592784770583</v>
+        <v>4367.592784770584</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>10176.2091419373</v>
+        <v>10176.20914193729</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>3718.424539440057</v>
@@ -30847,7 +30847,7 @@
         <v>3171.189177178967</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>51.03255827472313</v>
+        <v>51.03255827472316</v>
       </c>
       <c r="Y63" s="131" t="n">
         <v>4661.350612147648</v>
@@ -30916,10 +30916,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>4367.589286582866</v>
+        <v>4367.589286582867</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>4367.589286582866</v>
+        <v>4367.589286582867</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -31141,16 +31141,16 @@
         <v>0</v>
       </c>
       <c r="J67" s="139" t="n">
-        <v>32665.80535718387</v>
+        <v>32665.80535718386</v>
       </c>
       <c r="K67" s="140" t="n">
-        <v>14983.8247713327</v>
+        <v>14983.82477133271</v>
       </c>
       <c r="L67" s="140" t="n">
         <v>202.3739864950116</v>
       </c>
       <c r="M67" s="140" t="n">
-        <v>552.1088310115438</v>
+        <v>552.1088310115437</v>
       </c>
       <c r="N67" s="141" t="n">
         <v>48404.11294602312</v>
@@ -31165,10 +31165,10 @@
         <v>142.2558187419964</v>
       </c>
       <c r="S67" s="140" t="n">
-        <v>529.4434178862318</v>
+        <v>529.4434178862319</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>40480.89080031734</v>
+        <v>40480.89080031735</v>
       </c>
       <c r="V67" s="139" t="n">
         <v>27700.89671012674</v>
@@ -31237,19 +31237,19 @@
         <v>72370.99438301698</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>39238.32152279546</v>
+        <v>39238.32152279547</v>
       </c>
       <c r="Q68" s="143" t="n">
         <v>17647.25318436719</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>262.2537546686801</v>
+        <v>262.2537546686802</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>4897.646982133305</v>
+        <v>4897.646982133306</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>66413.0647305475</v>
+        <v>66413.06473054751</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>38240.73362856136</v>
@@ -31843,10 +31843,10 @@
         <v>0</v>
       </c>
       <c r="M77" s="131" t="n">
-        <v>0.7494770222813295</v>
+        <v>0.7494770222813296</v>
       </c>
       <c r="N77" s="132" t="n">
-        <v>0.7494770222813295</v>
+        <v>0.7494770222813296</v>
       </c>
       <c r="P77" s="130" t="n">
         <v>0</v>
@@ -31858,10 +31858,10 @@
         <v>0</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>0.8356985266883199</v>
+        <v>0.8356985266883201</v>
       </c>
       <c r="T77" s="132" t="n">
-        <v>0.8356985266883199</v>
+        <v>0.8356985266883201</v>
       </c>
       <c r="V77" s="130" t="n">
         <v>0</v>
@@ -31873,10 +31873,10 @@
         <v>0</v>
       </c>
       <c r="Y77" s="131" t="n">
-        <v>0.8963748172115763</v>
+        <v>0.8963748172115764</v>
       </c>
       <c r="Z77" s="132" t="n">
-        <v>0.8963748172115763</v>
+        <v>0.8963748172115764</v>
       </c>
     </row>
     <row r="78">
@@ -31931,7 +31931,7 @@
         <v>19.96087013213621</v>
       </c>
       <c r="V78" s="130" t="n">
-        <v>22.02775740512094</v>
+        <v>22.02775740512093</v>
       </c>
       <c r="W78" s="131" t="n">
         <v>0</v>
@@ -31943,7 +31943,7 @@
         <v>0</v>
       </c>
       <c r="Z78" s="132" t="n">
-        <v>22.02775740512094</v>
+        <v>22.02775740512093</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
@@ -31968,13 +31968,13 @@
         <v>4433</v>
       </c>
       <c r="J79" s="130" t="n">
-        <v>2476.941695579429</v>
+        <v>2476.941695579428</v>
       </c>
       <c r="K79" s="131" t="n">
         <v>2849.092396586792</v>
       </c>
       <c r="L79" s="131" t="n">
-        <v>11.82289063599359</v>
+        <v>11.8228906359936</v>
       </c>
       <c r="M79" s="131" t="n">
         <v>0</v>
@@ -31983,10 +31983,10 @@
         <v>5337.856982802215</v>
       </c>
       <c r="P79" s="130" t="n">
-        <v>2558.682056625252</v>
+        <v>2558.682056625253</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>2925.262718709261</v>
+        <v>2925.262718709262</v>
       </c>
       <c r="R79" s="131" t="n">
         <v>12.15252135439121</v>
@@ -31995,10 +31995,10 @@
         <v>0</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>5496.097296688905</v>
+        <v>5496.097296688907</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>2611.881295037886</v>
+        <v>2611.881295037884</v>
       </c>
       <c r="W79" s="131" t="n">
         <v>2984.036659919334</v>
@@ -32010,7 +32010,7 @@
         <v>0</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>5608.323959220914</v>
+        <v>5608.323959220912</v>
       </c>
     </row>
     <row r="80">
@@ -32111,10 +32111,10 @@
         <v>0</v>
       </c>
       <c r="M81" s="131" t="n">
-        <v>646.2757591213292</v>
+        <v>646.2757591213293</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>669.1214489585097</v>
+        <v>669.1214489585099</v>
       </c>
       <c r="P81" s="130" t="n">
         <v>35.63096672660322</v>
@@ -32141,10 +32141,10 @@
         <v>0</v>
       </c>
       <c r="Y81" s="131" t="n">
-        <v>880.0595490867236</v>
+        <v>880.0595490867238</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>933.776397082107</v>
+        <v>933.7763970821072</v>
       </c>
     </row>
     <row r="82">
@@ -32178,10 +32178,10 @@
         <v>0</v>
       </c>
       <c r="M82" s="134" t="n">
-        <v>646.2757591213292</v>
+        <v>646.2757591213293</v>
       </c>
       <c r="N82" s="135" t="n">
-        <v>646.2757591213292</v>
+        <v>646.2757591213293</v>
       </c>
       <c r="P82" s="133" t="n">
         <v>0</v>
@@ -32208,10 +32208,10 @@
         <v>0</v>
       </c>
       <c r="Y82" s="134" t="n">
-        <v>880.0595490867236</v>
+        <v>880.0595490867238</v>
       </c>
       <c r="Z82" s="135" t="n">
-        <v>880.0595490867236</v>
+        <v>880.0595490867238</v>
       </c>
     </row>
     <row r="83">
@@ -32450,7 +32450,7 @@
         <v>3895.860685324335</v>
       </c>
       <c r="M86" s="143" t="n">
-        <v>647.0252361436105</v>
+        <v>647.0252361436106</v>
       </c>
       <c r="N86" s="144" t="n">
         <v>496534.4141784618</v>
@@ -32480,10 +32480,10 @@
         <v>4038.865980466294</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>880.9559239039352</v>
+        <v>880.9559239039354</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>516784.425697706</v>
+        <v>516784.4256977059</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -32990,7 +32990,7 @@
         <v>0</v>
       </c>
       <c r="Q94" s="131" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="R94" s="131" t="n">
         <v>0</v>
@@ -32999,7 +32999,7 @@
         <v>0</v>
       </c>
       <c r="T94" s="132" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="V94" s="130" t="n">
         <v>0</v>
@@ -33054,7 +33054,7 @@
         <v>26.24432748303783</v>
       </c>
       <c r="P95" s="130" t="n">
-        <v>27.65663487526179</v>
+        <v>27.6566348752618</v>
       </c>
       <c r="Q95" s="131" t="n">
         <v>0</v>
@@ -33063,10 +33063,10 @@
         <v>0</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>1.4464780031783</v>
+        <v>1.446478003178301</v>
       </c>
       <c r="T95" s="132" t="n">
-        <v>29.10311287844009</v>
+        <v>29.1031128784401</v>
       </c>
       <c r="V95" s="130" t="n">
         <v>31.05175440243663</v>
@@ -33136,7 +33136,7 @@
         <v>26.57911917875575</v>
       </c>
       <c r="V96" s="130" t="n">
-        <v>28.06187153348852</v>
+        <v>28.06187153348851</v>
       </c>
       <c r="W96" s="131" t="n">
         <v>0</v>
@@ -33148,7 +33148,7 @@
         <v>0</v>
       </c>
       <c r="Z96" s="132" t="n">
-        <v>28.06187153348852</v>
+        <v>28.06187153348851</v>
       </c>
     </row>
     <row r="97">
@@ -33179,7 +33179,7 @@
         <v>6628.085294105205</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>81.12125915531612</v>
+        <v>81.12125915531614</v>
       </c>
       <c r="M97" s="131" t="n">
         <v>0</v>
@@ -33188,34 +33188,34 @@
         <v>15231.0221184335</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>8787.458946566274</v>
+        <v>8787.458946566276</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>6924.377261876312</v>
       </c>
       <c r="R97" s="131" t="n">
-        <v>85.73780046159801</v>
+        <v>85.73780046159803</v>
       </c>
       <c r="S97" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>15797.57400890418</v>
+        <v>15797.57400890419</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>9058.982559296477</v>
+        <v>9058.982559296473</v>
       </c>
       <c r="W97" s="131" t="n">
         <v>7214.103405258798</v>
       </c>
       <c r="X97" s="131" t="n">
-        <v>90.06841189161894</v>
+        <v>90.06841189161892</v>
       </c>
       <c r="Y97" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>16363.1543764469</v>
+        <v>16363.15437644689</v>
       </c>
     </row>
     <row r="98">
@@ -33255,13 +33255,13 @@
         <v>1051.558057647748</v>
       </c>
       <c r="P98" s="130" t="n">
-        <v>344.8677977438759</v>
+        <v>344.8677977438761</v>
       </c>
       <c r="Q98" s="131" t="n">
-        <v>695.6708181072373</v>
+        <v>695.6708181072372</v>
       </c>
       <c r="R98" s="131" t="n">
-        <v>4.376881306996877</v>
+        <v>4.376881306996878</v>
       </c>
       <c r="S98" s="131" t="n">
         <v>0</v>
@@ -33270,7 +33270,7 @@
         <v>1044.91549715811</v>
       </c>
       <c r="V98" s="130" t="n">
-        <v>337.2252462051626</v>
+        <v>337.2252462051625</v>
       </c>
       <c r="W98" s="131" t="n">
         <v>693.7423997998152</v>
@@ -33316,7 +33316,7 @@
         <v>34.42048685206373</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>4701.938698982582</v>
+        <v>4701.938698982581</v>
       </c>
       <c r="N99" s="132" t="n">
         <v>9591.082297490615</v>
@@ -33331,7 +33331,7 @@
         <v>42.03577551248054</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>5099.728555144815</v>
+        <v>5099.728555144816</v>
       </c>
       <c r="T99" s="132" t="n">
         <v>10943.97587903814</v>
@@ -33398,10 +33398,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>5099.725056957098</v>
+        <v>5099.725056957099</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>5099.725056957098</v>
+        <v>5099.725056957099</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -33588,7 +33588,7 @@
         <v>4086.411781183353</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>552.1088310115438</v>
+        <v>552.1088310115437</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>538270.4316285335</v>
@@ -33603,7 +33603,7 @@
         <v>4115.589524254454</v>
       </c>
       <c r="S103" s="140" t="n">
-        <v>529.4434178862318</v>
+        <v>529.4434178862319</v>
       </c>
       <c r="T103" s="141" t="n">
         <v>541818.6335051483</v>
@@ -33655,7 +33655,7 @@
         <v>4206.317514998797</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>5255.414666079997</v>
+        <v>5255.414666079996</v>
       </c>
       <c r="N104" s="144" t="n">
         <v>568905.4085614788</v>
@@ -33670,7 +33670,7 @@
         <v>4247.739981535529</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>5630.618451034225</v>
+        <v>5630.618451034226</v>
       </c>
       <c r="T104" s="144" t="n">
         <v>574767.6038082013</v>
@@ -33688,7 +33688,7 @@
         <v>6050.69352997534</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>581216.5896308239</v>
+        <v>581216.5896308238</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
